--- a/docs/downloads/经营分_山西省区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_山西省区_2026-10-18.xlsx
@@ -1054,14 +1054,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I6" t="n">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1089,7 +1089,7 @@
         <v>30</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
         <v>20</v>
@@ -1113,27 +1113,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>阳泉市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7380971667918424127</t>
+          <t>7391792608135088166</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0阳泉广阳路中图商贸港店）</t>
+          <t>7天酒店（长治壶关新建路人民医院店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>维也纳酒店(广阳路店)</t>
+          <t>7天酒店(长治壶关新建路人民医院店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1201,27 +1201,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>阳泉市</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6601161011175098375</t>
+          <t>7380971667918424127</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>锦江之星(吕梁长治路酒店)</t>
+          <t>维也纳酒店（5.0阳泉广阳路中图商贸港店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>锦江之星(吕梁长治路酒店)</t>
+          <t>维也纳酒店(广阳路店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1289,27 +1289,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6601143093150353411</t>
+          <t>6601161011175098375</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>锦江之星（太原万达广场龙潭公园店）</t>
+          <t>锦江之星(吕梁长治路酒店)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>锦江之星(太原龙潭公园店)</t>
+          <t>锦江之星(吕梁长治路酒店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1321,7 +1321,7 @@
         <v>70</v>
       </c>
       <c r="I9" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7456750716481177654</t>
+          <t>6601143093150353411</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>维也纳酒店（太原尖草坪区政府省人民医院天美杉杉奥莱店）</t>
+          <t>锦江之星（太原万达广场龙潭公园店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>维也纳酒店(太原尖草坪区政府省人民医院天美杉杉奥莱店)</t>
+          <t>锦江之星(太原龙潭公园店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1406,14 +1406,14 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>-25</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1423,25 +1423,25 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="n">
         <v>20</v>
@@ -1465,27 +1465,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6601168613967661063</t>
+          <t>7456750716481177654</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7天酒店（临汾火车站店）</t>
+          <t>维也纳酒店（太原尖草坪区政府省人民医院天美杉杉奥莱店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7天酒店(临汾火车站店)</t>
+          <t>维也纳酒店(太原尖草坪区政府省人民医院天美杉杉奥莱店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1494,14 +1494,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1511,13 +1511,13 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
@@ -1529,7 +1529,7 @@
         <v>30</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="n">
         <v>20</v>
@@ -1553,39 +1553,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7391792608135088166</t>
+          <t>6601168613967661063</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7天酒店（长治壶关新建路人民医院店）</t>
+          <t>7天酒店（临汾火车站店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7天酒店(长治壶关新建路人民医院店)</t>
+          <t>7天酒店(临汾火车站店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>75</v>
       </c>
       <c r="I12" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2355,33 +2355,33 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7544177702270404651</t>
+          <t>6679982931873712136</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IU酒店（太原山大一院迎泽公园店）</t>
+          <t>IU酒店(太原千峰南路店)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>iu酒店(山大一院迎泽公园店)</t>
+          <t>iu酒店(太原千峰南路店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2391,25 +2391,25 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="n">
         <v>20</v>
@@ -2433,27 +2433,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6601141576905279495</t>
+          <t>7357231867210237993</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7天优品（临汾生龙国际鼓楼东大街店）</t>
+          <t>IU酒店（大同西环路大润发店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7天优品酒店(临汾鼓楼东大街店)</t>
+          <t>IU酒店(大同西环路大润发店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2465,11 +2465,11 @@
         <v>85</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>-30</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2479,13 +2479,13 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6679982931873712136</t>
+          <t>7044370571840194568</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IU酒店(太原千峰南路店)</t>
+          <t>希岸·轻雅酒店(太原柳巷大南门地铁站店)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>iu酒店(太原千峰南路店)</t>
+          <t>希岸·轻雅酒店(太原柳巷大南门地铁站店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2553,7 +2553,7 @@
         <v>85</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
@@ -2579,7 +2579,7 @@
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
         <v>30</v>
@@ -2609,27 +2609,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>山西北片区</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>大同市</t>
-        </is>
-      </c>
+          <t>山西东片区</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7357231867210237993</t>
+          <t>7543445920772278322</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IU酒店（大同西环路大润发店）</t>
+          <t>潮漫酒店（太原火车站服装城五一广场店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IU酒店(大同西环路大润发店)</t>
+          <t>潮漫酒店(太原火车站五一广场店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2641,11 +2637,11 @@
         <v>85</v>
       </c>
       <c r="I24" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2655,19 +2651,19 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
+        <v>30</v>
+      </c>
+      <c r="N24" t="n">
+        <v>30</v>
+      </c>
+      <c r="O24" t="n">
+        <v>25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>30</v>
-      </c>
-      <c r="O24" t="n">
-        <v>30</v>
-      </c>
-      <c r="P24" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>25</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2697,27 +2693,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7044370571840194568</t>
+          <t>7289447960751671348</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(太原柳巷大南门地铁站店)</t>
+          <t>白玉兰商务酒店（忻州宁武滨河花园店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(太原柳巷大南门地铁站店)</t>
+          <t>白玉兰(商务)酒店忻州宁武滨河花园店</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2729,7 +2725,7 @@
         <v>85</v>
       </c>
       <c r="I25" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2743,7 +2739,7 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
@@ -2755,7 +2751,7 @@
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -2785,23 +2781,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>山西东片区</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>山西北片区</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>大同市</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7543445920772278322</t>
+          <t>7494467627922753555</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>潮漫酒店（太原火车站服装城五一广场店）</t>
+          <t>锦江之星(大同古城华严寺酒店)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>潮漫酒店(太原火车站五一广场店)</t>
+          <t>锦江之星(大同古城武定门酒店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2813,11 +2813,11 @@
         <v>85</v>
       </c>
       <c r="I26" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2827,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2839,7 +2839,7 @@
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2874,22 +2874,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7289447960751671348</t>
+          <t>7081220555378001960</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（忻州宁武滨河花园店）</t>
+          <t>7天优品（大同第五人民医院店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>白玉兰(商务)酒店忻州宁武滨河花园店</t>
+          <t>7天优品酒店(大同第五人民医院店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2898,24 +2898,24 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
@@ -2957,71 +2957,71 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7081220555378001960</t>
+          <t>7544177702270404651</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7天优品（大同第五人民医院店）</t>
+          <t>IU酒店（太原山大一院迎泽公园店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7天优品酒店(大同第五人民医院店)</t>
+          <t>iu酒店(山大一院迎泽公园店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>86</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
       </c>
       <c r="M28" t="n">
+        <v>14</v>
+      </c>
+      <c r="N28" t="n">
+        <v>30</v>
+      </c>
+      <c r="O28" t="n">
         <v>25</v>
       </c>
-      <c r="N28" t="n">
-        <v>30</v>
-      </c>
-      <c r="O28" t="n">
-        <v>20</v>
-      </c>
       <c r="P28" t="n">
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T28" t="n">
         <v>20</v>
@@ -3048,20 +3048,24 @@
           <t>山西中片区</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>长治市</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6601152258656716808</t>
+          <t>7234811569874405410</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7天酒店(长治西大街上党门店)</t>
+          <t>7天酒店（长治长子鹿谷大街体育馆店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7天连锁酒店(长治西大街上党门店)</t>
+          <t>7天酒店(长治长子路谷大街体育馆店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3077,7 +3081,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3087,13 +3091,13 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
@@ -3129,32 +3133,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7234811569874405410</t>
+          <t>7236636263678216252</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7天酒店（长治长子鹿谷大街体育馆店）</t>
+          <t>喆啡酒店(太原南站山西大学店)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7天酒店(长治长子路谷大街体育馆店)</t>
+          <t>喆啡酒店(太原火车南站山西大学店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3181,13 +3185,13 @@
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3217,27 +3221,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7412164612600924196</t>
+          <t>6838439008805079043</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>丽怡酒店（运城星河广场店）</t>
+          <t>希岸酒店(太原火车站五一广场店)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>丽怡酒店(运城星河广场店)</t>
+          <t>希岸酒店(太原火车站五一广场店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3263,7 +3267,7 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
         <v>30</v>
@@ -3275,7 +3279,7 @@
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3315,17 +3319,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>7236636263678216252</t>
+          <t>6601147462038063108</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>喆啡酒店(太原南站山西大学店)</t>
+          <t>希岸酒店（太原南内环店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>喆啡酒店(太原火车南站山西大学店)</t>
+          <t>希岸酒店(太原南内环省人民医院店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3393,27 +3397,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>6838439008805079043</t>
+          <t>6988348997492541453</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>希岸酒店(太原火车站五一广场店)</t>
+          <t>维也纳3好酒店（山西晋中市寿阳朝阳阁店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>希岸酒店(太原火车站五一广场店)</t>
+          <t>维也纳3好酒店(山西晋中市寿阳朝阳阁店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3439,7 +3443,7 @@
         <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N33" t="n">
         <v>30</v>
@@ -3451,7 +3455,7 @@
         <v>30</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R33" t="n">
         <v>30</v>
@@ -3481,32 +3485,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>6601147462038063108</t>
+          <t>6785296357017126923</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>希岸酒店（太原南内环店）</t>
+          <t>锦江之星品尚(大同火车站酒店)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>希岸酒店(太原南内环省人民医院店)</t>
+          <t>锦江之星品尚(大同火车站店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3569,39 +3573,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>6988348997492541453</t>
+          <t>7205785499250739240</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（山西晋中市寿阳朝阳阁店）</t>
+          <t>非繁城品酒店(运城南风广场地矿店)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(山西晋中市寿阳朝阳阁店)</t>
+          <t>非繁城品(运城南风广场地矿店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>87</v>
       </c>
       <c r="I35" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3621,13 +3625,13 @@
         <v>30</v>
       </c>
       <c r="O35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P35" t="n">
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
@@ -3657,27 +3661,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>6785296357017126923</t>
+          <t>7503744484267313152</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>锦江之星品尚(大同火车站酒店)</t>
+          <t>麗枫酒店（临汾洪洞大槐树店）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>锦江之星品尚(大同火车站店)</t>
+          <t>麗枫酒店(临汾洪洞大槐树景区店)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3689,7 +3693,7 @@
         <v>87</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3745,27 +3749,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>7205785499250739240</t>
+          <t>7626244734908860451</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>非繁城品酒店(运城南风广场地矿店)</t>
+          <t>麗枫酒店（浑源古城悬空寺店）</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>非繁城品(运城南风广场地矿店)</t>
+          <t>麗枫酒店(浑源古城悬空寺店)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3774,10 +3778,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3791,7 +3795,7 @@
         <v>10</v>
       </c>
       <c r="M37" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N37" t="n">
         <v>30</v>
@@ -3803,7 +3807,7 @@
         <v>30</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R37" t="n">
         <v>30</v>
@@ -3833,27 +3837,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>7503744484267313152</t>
+          <t>7034175197259237411</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>麗枫酒店（临汾洪洞大槐树店）</t>
+          <t>7天优品Premium（太原晋祠公园店）</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>麗枫酒店(临汾洪洞大槐树景区店)</t>
+          <t>7天优品酒店(晋祠公园店)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3862,10 +3866,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I38" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3879,7 +3883,7 @@
         <v>10</v>
       </c>
       <c r="M38" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N38" t="n">
         <v>30</v>
@@ -3921,27 +3925,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>7626244734908860451</t>
+          <t>6601141576905279495</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>麗枫酒店（浑源古城悬空寺店）</t>
+          <t>7天优品（临汾生龙国际鼓楼东大街店）</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>麗枫酒店(浑源古城悬空寺店)</t>
+          <t>7天优品酒店(临汾鼓楼东大街店)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3950,10 +3954,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3967,7 +3971,7 @@
         <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N39" t="n">
         <v>30</v>
@@ -3979,7 +3983,7 @@
         <v>30</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R39" t="n">
         <v>30</v>
@@ -4009,7 +4013,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4019,22 +4023,22 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>7034175197259237411</t>
+          <t>7436088520130693156</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7天优品Premium（太原晋祠公园店）</t>
+          <t>7天优品（太原南内环地铁站老军营小吃街店）</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7天优品酒店(晋祠公园店)</t>
+          <t>7天优品(太原南内环街地铁站店)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -4097,27 +4101,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>7035911118157514784</t>
+          <t>7581298849579436066</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7天优品Premium（市政府大同大学店）</t>
+          <t>7天智选酒店（运城七彩盐湖盬街店）</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>7天优品Premium(市政府大同大学店)</t>
+          <t>7天智选酒店(运城七彩盐湖盬街店)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4129,7 +4133,7 @@
         <v>90</v>
       </c>
       <c r="I41" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -4143,19 +4147,19 @@
         <v>10</v>
       </c>
       <c r="M41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N41" t="n">
         <v>30</v>
       </c>
       <c r="O41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P41" t="n">
         <v>30</v>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R41" t="n">
         <v>30</v>
@@ -4185,39 +4189,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>7436088520130693156</t>
+          <t>7122789583427012622</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7天优品（太原南内环地铁站老军营小吃街店）</t>
+          <t>7天酒店（新7天长治屯留会堂店）</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7天优品(太原南内环街地铁站店)</t>
+          <t>7天酒店(长治屯留会堂店)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H42" t="n">
         <v>90</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -4231,19 +4235,19 @@
         <v>10</v>
       </c>
       <c r="M42" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" t="n">
+        <v>30</v>
+      </c>
+      <c r="O42" t="n">
         <v>25</v>
       </c>
-      <c r="N42" t="n">
-        <v>30</v>
-      </c>
-      <c r="O42" t="n">
-        <v>20</v>
-      </c>
       <c r="P42" t="n">
         <v>30</v>
       </c>
       <c r="Q42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R42" t="n">
         <v>30</v>
@@ -4273,27 +4277,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>7581298849579436066</t>
+          <t>6601190874749601800</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7天智选酒店（运城七彩盐湖盬街店）</t>
+          <t>7天酒店（长治沁县店）</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7天智选酒店(运城七彩盐湖盬街店)</t>
+          <t>7天连锁酒店(沁县店)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4305,7 +4309,7 @@
         <v>90</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -4361,39 +4365,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>7122789583427012622</t>
+          <t>7233737738418145340</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7天酒店（新7天长治屯留会堂店）</t>
+          <t>IU酒店(运城永济迎宾路福茂骨科医院店)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>7天酒店(长治屯留会堂店)</t>
+          <t>IU酒店(运城永济迎宾路福茂骨科医院店)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H44" t="n">
         <v>90</v>
       </c>
       <c r="I44" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -4407,19 +4411,19 @@
         <v>10</v>
       </c>
       <c r="M44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N44" t="n">
         <v>30</v>
       </c>
       <c r="O44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P44" t="n">
         <v>30</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R44" t="n">
         <v>30</v>
@@ -4454,22 +4458,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>6601190874749601800</t>
+          <t>7326770712952178688</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7天酒店（长治沁县店）</t>
+          <t>IU酒店（晋中榆次五中万达广场店）</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7天连锁酒店(沁县店)</t>
+          <t>IU酒店(晋中榆次五中万达广场店)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4481,7 +4485,7 @@
         <v>90</v>
       </c>
       <c r="I45" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -4495,7 +4499,7 @@
         <v>10</v>
       </c>
       <c r="M45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N45" t="n">
         <v>30</v>
@@ -4507,7 +4511,7 @@
         <v>30</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R45" t="n">
         <v>30</v>
@@ -4537,32 +4541,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>阳泉市</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>7233737738418145340</t>
+          <t>6644006626867169287</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IU酒店(运城永济迎宾路福茂骨科医院店)</t>
+          <t>IU酒店（阳泉新建街天桥店）</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>IU酒店(运城永济迎宾路福茂骨科医院店)</t>
+          <t>iu酒店(阳泉新建街天桥店)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -4625,43 +4629,43 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>7326770712952178688</t>
+          <t>7485253882780583990</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IU酒店（晋中榆次五中万达广场店）</t>
+          <t>喆啡酒店(4.0大同古城店)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>IU酒店(晋中榆次五中万达广场店)</t>
+          <t>喆啡酒店(4.0大同古城店)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>90</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -4671,7 +4675,7 @@
         <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N47" t="n">
         <v>30</v>
@@ -4683,7 +4687,7 @@
         <v>30</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R47" t="n">
         <v>30</v>
@@ -4713,27 +4717,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>阳泉市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>6644006626867169287</t>
+          <t>6756124064592545806</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IU酒店（阳泉新建街天桥店）</t>
+          <t>希岸酒店(长治城隍庙店)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>iu酒店(阳泉新建街天桥店)</t>
+          <t>希岸酒店(长治城隍庙店)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4745,7 +4749,7 @@
         <v>90</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -4759,7 +4763,7 @@
         <v>10</v>
       </c>
       <c r="M48" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N48" t="n">
         <v>30</v>
@@ -4771,7 +4775,7 @@
         <v>30</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R48" t="n">
         <v>30</v>
@@ -4801,27 +4805,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>7485253882780583990</t>
+          <t>7231475196660549692</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>喆啡酒店(4.0大同古城店)</t>
+          <t>希岸酒店（太原南站武宿机场富士康南门店）</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>喆啡酒店(4.0大同古城店)</t>
+          <t>希岸酒店(太原武宿机场富士康南门店)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4837,7 +4841,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -4847,13 +4851,13 @@
         <v>10</v>
       </c>
       <c r="M49" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N49" t="n">
         <v>30</v>
       </c>
       <c r="O49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P49" t="n">
         <v>30</v>
@@ -4889,39 +4893,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>7231475196660549692</t>
+          <t>7234810698226731008</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>希岸酒店（太原南站武宿机场富士康南门店）</t>
+          <t>希岸酒店（忻州繁峙县政府店）</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>希岸酒店(太原武宿机场富士康南门店)</t>
+          <t>希岸酒店(忻州繁峙县政府店)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H50" t="n">
         <v>90</v>
       </c>
       <c r="I50" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -4941,13 +4945,13 @@
         <v>30</v>
       </c>
       <c r="O50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P50" t="n">
         <v>30</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R50" t="n">
         <v>30</v>
@@ -4982,22 +4986,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>7234810698226731008</t>
+          <t>7034742418826070031</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>希岸酒店（忻州繁峙县政府店）</t>
+          <t>潮漫酒店(大同广灵店)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>希岸酒店(忻州繁峙县政府店)</t>
+          <t>潮漫酒店(大同广灵店)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5065,39 +5069,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>7034742418826070031</t>
+          <t>7239588777046313015</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>潮漫酒店(大同广灵店)</t>
+          <t>白玉兰商务酒店(晋中寿阳植物园店)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>潮漫酒店(大同广灵店)</t>
+          <t>白玉兰商务酒店(晋中寿阳植物园店)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H52" t="n">
         <v>90</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -5117,13 +5121,13 @@
         <v>30</v>
       </c>
       <c r="O52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P52" t="n">
         <v>30</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R52" t="n">
         <v>30</v>
@@ -5153,39 +5157,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>7239588777046313015</t>
+          <t>6745992868227270664</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(晋中寿阳植物园店)</t>
+          <t>维也纳3好酒店（太原高铁站长风街店）</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(晋中寿阳植物园店)</t>
+          <t>维也纳3好酒店(太原高铁站长风街店)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H53" t="n">
         <v>90</v>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -5205,13 +5209,13 @@
         <v>30</v>
       </c>
       <c r="O53" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P53" t="n">
         <v>30</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
         <v>30</v>
@@ -5241,27 +5245,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>6745992868227270664</t>
+          <t>7411758004451674152</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（太原高铁站长风街店）</t>
+          <t>维也纳国际酒店（5.0河津龙门大道店）</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(太原高铁站长风街店)</t>
+          <t>维也纳国际酒店(河津龙门大道店)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5273,7 +5277,7 @@
         <v>90</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -5287,19 +5291,19 @@
         <v>10</v>
       </c>
       <c r="M54" t="n">
+        <v>15</v>
+      </c>
+      <c r="N54" t="n">
+        <v>30</v>
+      </c>
+      <c r="O54" t="n">
         <v>25</v>
       </c>
-      <c r="N54" t="n">
-        <v>30</v>
-      </c>
-      <c r="O54" t="n">
-        <v>20</v>
-      </c>
       <c r="P54" t="n">
         <v>30</v>
       </c>
       <c r="Q54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R54" t="n">
         <v>30</v>
@@ -5329,39 +5333,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>7411758004451674152</t>
+          <t>7210372188010973187</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0河津龙门大道店）</t>
+          <t>维也纳酒店（5.0太原火车站服装城店）</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(河津龙门大道店)</t>
+          <t>维也纳酒店(山西太原火车站服装城店)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>90</v>
       </c>
       <c r="I55" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -5375,13 +5379,13 @@
         <v>10</v>
       </c>
       <c r="M55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N55" t="n">
         <v>30</v>
       </c>
       <c r="O55" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P55" t="n">
         <v>30</v>
@@ -5417,43 +5421,43 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>7210372188010973187</t>
+          <t>7557108285954869287</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0太原火车站服装城店）</t>
+          <t>维也纳酒店（孝义万达广场市政府店）</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>维也纳酒店(山西太原火车站服装城店)</t>
+          <t>维也纳酒店(孝义万达广场市政府店)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>90</v>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -5463,7 +5467,7 @@
         <v>10</v>
       </c>
       <c r="M56" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N56" t="n">
         <v>30</v>
@@ -5475,7 +5479,7 @@
         <v>30</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R56" t="n">
         <v>30</v>
@@ -5505,27 +5509,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>7557108285954869287</t>
+          <t>6601148840277968909</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>维也纳酒店（孝义万达广场市政府店）</t>
+          <t>锦江之星(大同古城平城桥店)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>维也纳酒店(孝义万达广场市政府店)</t>
+          <t>锦江之星酒店(平城桥店)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5541,7 +5545,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -5551,7 +5555,7 @@
         <v>10</v>
       </c>
       <c r="M57" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N57" t="n">
         <v>30</v>
@@ -5563,7 +5567,7 @@
         <v>30</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R57" t="n">
         <v>30</v>
@@ -5593,39 +5597,35 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>山西北片区</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>大同市</t>
-        </is>
-      </c>
+          <t>山西西片区</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>7494467627922753555</t>
+          <t>7176871801337677857</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>锦江之星(大同古城华严寺酒店)</t>
+          <t>锦江之星酒店(汾阳市英雄中路店)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>锦江之星(大同古城武定门酒店)</t>
+          <t>锦江之星酒店(汾阳市英雄中路店)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H58" t="n">
         <v>90</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -5639,19 +5639,19 @@
         <v>10</v>
       </c>
       <c r="M58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N58" t="n">
         <v>30</v>
       </c>
       <c r="O58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P58" t="n">
         <v>30</v>
       </c>
       <c r="Q58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R58" t="n">
         <v>30</v>
@@ -5681,65 +5681,65 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>6601148840277968909</t>
+          <t>7023700200262731789</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>锦江之星(大同古城平城桥店)</t>
+          <t>锦江都城酒店(晋中奥特莱斯万达广场店)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>锦江之星酒店(平城桥店)</t>
+          <t>锦江都城酒店(晋中奥特莱斯万达广场店)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>90</v>
       </c>
       <c r="I59" t="n">
+        <v>-30</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>稳房源</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>10</v>
+      </c>
+      <c r="L59" t="n">
+        <v>10</v>
+      </c>
+      <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>稳房源,提质量,拿收益</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>10</v>
-      </c>
-      <c r="L59" t="n">
-        <v>10</v>
-      </c>
-      <c r="M59" t="n">
-        <v>20</v>
-      </c>
       <c r="N59" t="n">
         <v>30</v>
       </c>
       <c r="O59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P59" t="n">
         <v>30</v>
       </c>
       <c r="Q59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R59" t="n">
         <v>30</v>
@@ -5779,17 +5779,17 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>6601138073352800270</t>
+          <t>6601139644534884366</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>锦江之星品尚(太原平阳路店)</t>
+          <t>锦江都城酒店（太原茂业天地长风街地铁站店）</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>锦江之星品尚酒店(太原平阳路店)</t>
+          <t>锦江都城酒店(太原长风街地铁站店)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5801,7 +5801,7 @@
         <v>90</v>
       </c>
       <c r="I60" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -5860,20 +5860,24 @@
           <t>山西西片区</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>吕梁市</t>
+        </is>
+      </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>7176871801337677857</t>
+          <t>7455573490079369243</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>锦江之星酒店(汾阳市英雄中路店)</t>
+          <t>麗枫酒店(吕梁龙凤南大街世纪广场店)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>锦江之星酒店(汾阳市英雄中路店)</t>
+          <t>麗枫酒店(吕梁龙凤南大街世纪广场店)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5885,7 +5889,7 @@
         <v>90</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -5905,13 +5909,13 @@
         <v>30</v>
       </c>
       <c r="O61" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P61" t="n">
         <v>30</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R61" t="n">
         <v>30</v>
@@ -5951,33 +5955,33 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>7023700200262731789</t>
+          <t>6741342475543250951</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>锦江都城酒店(晋中奥特莱斯万达广场店)</t>
+          <t>麗枫酒店(平遥古城又见平遥店)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>锦江都城酒店(晋中奥特莱斯万达广场店)</t>
+          <t>麗枫酒店(平遥又见平遥店)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H62" t="n">
         <v>90</v>
       </c>
       <c r="I62" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -5987,19 +5991,19 @@
         <v>10</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N62" t="n">
         <v>30</v>
       </c>
       <c r="O62" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P62" t="n">
         <v>30</v>
       </c>
       <c r="Q62" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="R62" t="n">
         <v>30</v>
@@ -6029,27 +6033,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>6601139644534884366</t>
+          <t>7168715561759672355</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>锦江都城酒店（太原茂业天地长风街地铁站店）</t>
+          <t>7天酒店（太谷西站店）</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>锦江都城酒店(太原长风街地铁站店)</t>
+          <t>7天酒店(太谷西站店)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6058,18 +6062,18 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
         <v>10</v>
@@ -6087,7 +6091,7 @@
         <v>30</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R63" t="n">
         <v>30</v>
@@ -6117,27 +6121,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>山西西片区</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>吕梁市</t>
-        </is>
-      </c>
+          <t>山西中片区</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>7455573490079369243</t>
+          <t>6601152258656716808</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>麗枫酒店(吕梁龙凤南大街世纪广场店)</t>
+          <t>7天酒店(长治西大街上党门店)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>麗枫酒店(吕梁龙凤南大街世纪广场店)</t>
+          <t>7天连锁酒店(长治西大街上党门店)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6146,14 +6146,14 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -6163,13 +6163,13 @@
         <v>10</v>
       </c>
       <c r="M64" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N64" t="n">
         <v>30</v>
       </c>
       <c r="O64" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P64" t="n">
         <v>30</v>
@@ -6205,39 +6205,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>6741342475543250951</t>
+          <t>6601150433513703437</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>麗枫酒店(平遥古城又见平遥店)</t>
+          <t>7天酒店（太原火车站服装城省人民医院店）</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>麗枫酒店(平遥又见平遥店)</t>
+          <t>7天酒店(太原火车站店)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>10</v>
       </c>
       <c r="M65" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N65" t="n">
         <v>30</v>
@@ -6263,7 +6263,7 @@
         <v>30</v>
       </c>
       <c r="Q65" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R65" t="n">
         <v>30</v>
@@ -6293,65 +6293,65 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>7168715561759672355</t>
+          <t>7412164612600924196</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7天酒店（太谷西站店）</t>
+          <t>丽怡酒店（运城星河广场店）</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>7天酒店(太谷西站店)</t>
+          <t>丽怡酒店(运城星河广场店)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L66" t="n">
         <v>10</v>
       </c>
       <c r="M66" t="n">
+        <v>22</v>
+      </c>
+      <c r="N66" t="n">
+        <v>30</v>
+      </c>
+      <c r="O66" t="n">
         <v>25</v>
       </c>
-      <c r="N66" t="n">
-        <v>30</v>
-      </c>
-      <c r="O66" t="n">
-        <v>20</v>
-      </c>
       <c r="P66" t="n">
         <v>30</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R66" t="n">
         <v>30</v>
@@ -6381,27 +6381,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>6601150433513703437</t>
+          <t>6601135743966382093</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7天酒店（太原火车站服装城省人民医院店）</t>
+          <t>希岸酒店(晋中大学城万达店)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7天酒店(太原火车站店)</t>
+          <t>希岸酒店(晋中大学城万达店)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6413,7 +6413,7 @@
         <v>92</v>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -6433,13 +6433,13 @@
         <v>30</v>
       </c>
       <c r="O67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P67" t="n">
         <v>30</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R67" t="n">
         <v>30</v>
@@ -6469,27 +6469,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>山西中片区</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>晋中市</t>
-        </is>
-      </c>
+          <t>山西西片区</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>6601135743966382093</t>
+          <t>7537106907102709779</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>希岸酒店(晋中大学城万达店)</t>
+          <t>潮漫酒店(太原龙城大街高铁南站机场店)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>希岸酒店(晋中大学城万达店)</t>
+          <t>潮漫酒店(太原龙城大街高铁南站机场店)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6501,11 +6497,11 @@
         <v>92</v>
       </c>
       <c r="I68" t="n">
-        <v>-5</v>
+        <v>27</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -6515,25 +6511,25 @@
         <v>10</v>
       </c>
       <c r="M68" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N68" t="n">
         <v>30</v>
       </c>
       <c r="O68" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P68" t="n">
         <v>30</v>
       </c>
       <c r="Q68" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R68" t="n">
         <v>30</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T68" t="n">
         <v>20</v>
@@ -6557,23 +6553,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>山西西片区</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>山西南片区</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>运城市</t>
+        </is>
+      </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>7537106907102709779</t>
+          <t>7457036946171234315</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>潮漫酒店(太原龙城大街高铁南站机场店)</t>
+          <t>维也纳酒店（5.0 运城绛县金御国际店）</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>潮漫酒店(太原龙城大街高铁南站机场店)</t>
+          <t>维也纳酒店(绛县店)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6585,11 +6585,11 @@
         <v>92</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -6599,25 +6599,25 @@
         <v>10</v>
       </c>
       <c r="M69" t="n">
+        <v>22</v>
+      </c>
+      <c r="N69" t="n">
+        <v>30</v>
+      </c>
+      <c r="O69" t="n">
         <v>25</v>
       </c>
-      <c r="N69" t="n">
-        <v>30</v>
-      </c>
-      <c r="O69" t="n">
-        <v>20</v>
-      </c>
       <c r="P69" t="n">
         <v>30</v>
       </c>
       <c r="Q69" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R69" t="n">
         <v>30</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T69" t="n">
         <v>20</v>
@@ -6651,29 +6651,29 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>7457036946171234315</t>
+          <t>6601250897500571652</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0 运城绛县金御国际店）</t>
+          <t>维也纳酒店（山西运城槐东路店）</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>维也纳酒店(绛县店)</t>
+          <t>维也纳酒店(山西运城槐东路店)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H70" t="n">
         <v>92</v>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6693,13 +6693,13 @@
         <v>30</v>
       </c>
       <c r="O70" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P70" t="n">
         <v>30</v>
       </c>
       <c r="Q70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R70" t="n">
         <v>30</v>
@@ -6729,39 +6729,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>6601250897500571652</t>
+          <t>7289316507207600147</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>维也纳酒店（山西运城槐东路店）</t>
+          <t>麗枫酒店 (太原南站山西大学店)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>维也纳酒店(山西运城槐东路店)</t>
+          <t>麗枫酒店(太原南站山西大学店)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>92</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -6817,27 +6817,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>7289316507207600147</t>
+          <t>7546085742750779430</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>麗枫酒店 (太原南站山西大学店)</t>
+          <t>麗枫酒店（晋中太谷金谷广场店）</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>麗枫酒店(太原南站山西大学店)</t>
+          <t>麗枫酒店(晋中太谷金谷广场店)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6849,11 +6849,11 @@
         <v>92</v>
       </c>
       <c r="I72" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -6863,7 +6863,7 @@
         <v>10</v>
       </c>
       <c r="M72" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N72" t="n">
         <v>30</v>
@@ -6881,7 +6881,7 @@
         <v>30</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T72" t="n">
         <v>20</v>
@@ -6905,27 +6905,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>7546085742750779430</t>
+          <t>7119712778306357261</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>麗枫酒店（晋中太谷金谷广场店）</t>
+          <t>7天优品Premium（山西临汾解放东路店）</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>麗枫酒店(晋中太谷金谷广场店)</t>
+          <t>7天优品Premium(山西临汾解放东路店)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6934,14 +6934,14 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -6951,25 +6951,25 @@
         <v>10</v>
       </c>
       <c r="M73" t="n">
+        <v>20</v>
+      </c>
+      <c r="N73" t="n">
+        <v>30</v>
+      </c>
+      <c r="O73" t="n">
+        <v>20</v>
+      </c>
+      <c r="P73" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q73" t="n">
         <v>25</v>
       </c>
-      <c r="N73" t="n">
-        <v>30</v>
-      </c>
-      <c r="O73" t="n">
-        <v>20</v>
-      </c>
-      <c r="P73" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>20</v>
-      </c>
       <c r="R73" t="n">
         <v>30</v>
       </c>
       <c r="S73" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T73" t="n">
         <v>20</v>
@@ -6993,32 +6993,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>7119712778306357261</t>
+          <t>7035911118157514784</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7天优品Premium（山西临汾解放东路店）</t>
+          <t>7天优品Premium（市政府大同大学店）</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>7天优品Premium(山西临汾解放东路店)</t>
+          <t>7天优品Premium(市政府大同大学店)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -7039,19 +7039,19 @@
         <v>10</v>
       </c>
       <c r="M74" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N74" t="n">
         <v>30</v>
       </c>
       <c r="O74" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P74" t="n">
         <v>30</v>
       </c>
       <c r="Q74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R74" t="n">
         <v>30</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -7697,27 +7697,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>7133762821522720772</t>
+          <t>7418425551997650980</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>丽怡酒店（侯马新田广场店）</t>
+          <t>IU酒店（长治通天峡景区店）</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>丽怡酒店(侯马新田广场店)</t>
+          <t>IU酒店(长治通天峡景区店)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7729,11 +7729,11 @@
         <v>95</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -7743,19 +7743,19 @@
         <v>10</v>
       </c>
       <c r="M82" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N82" t="n">
         <v>30</v>
       </c>
       <c r="O82" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P82" t="n">
         <v>30</v>
       </c>
       <c r="Q82" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R82" t="n">
         <v>30</v>
@@ -7785,32 +7785,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>6756124064592545806</t>
+          <t>7133762821522720772</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>希岸酒店(长治城隍庙店)</t>
+          <t>丽怡酒店（侯马新田广场店）</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>希岸酒店(长治城隍庙店)</t>
+          <t>丽怡酒店(侯马新田广场店)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -7831,13 +7831,13 @@
         <v>10</v>
       </c>
       <c r="M83" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N83" t="n">
         <v>30</v>
       </c>
       <c r="O83" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P83" t="n">
         <v>30</v>
@@ -8137,27 +8137,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>6919967936090228750</t>
+          <t>7370927881465104420</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（大同古城华严寺店）</t>
+          <t>维也纳3好酒店（晋中榆社文峰塔店）</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(大同古城店)</t>
+          <t>维也纳3好酒店(榆社店)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8169,7 +8169,7 @@
         <v>95</v>
       </c>
       <c r="I87" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -8225,43 +8225,43 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>7370927881465104420</t>
+          <t>6601139359590647816</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（晋中榆社文峰塔店）</t>
+          <t>维也纳智好酒店（山西侯马金钻店）</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(榆社店)</t>
+          <t>维也纳智好酒店(山西侯马金钻店)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H88" t="n">
         <v>95</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -8271,13 +8271,13 @@
         <v>10</v>
       </c>
       <c r="M88" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N88" t="n">
         <v>30</v>
       </c>
       <c r="O88" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P88" t="n">
         <v>30</v>
@@ -8313,27 +8313,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>6601139359590647816</t>
+          <t>6954291220742932518</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（山西侯马金钻店）</t>
+          <t>维也纳智好酒店（山西师范武宿机场店）</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(山西侯马金钻店)</t>
+          <t>维也纳智好酒店(山西榆次大学城店)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8345,7 +8345,7 @@
         <v>95</v>
       </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -8411,17 +8411,17 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>6954291220742932518</t>
+          <t>7099019942820841472</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（山西师范武宿机场店）</t>
+          <t>维也纳酒店（5.0晋中大学城店）</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(山西榆次大学城店)</t>
+          <t>维也纳酒店5.0山西晋中大学城店</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8433,7 +8433,7 @@
         <v>95</v>
       </c>
       <c r="I90" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -8489,32 +8489,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>7099019942820841472</t>
+          <t>7278642452473317415</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0晋中大学城店）</t>
+          <t>维也纳酒店（5.0运城河东街万达店）</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>维也纳酒店5.0山西晋中大学城店</t>
+          <t>维也纳酒店(山西运城河东街万达店)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -8535,13 +8535,13 @@
         <v>10</v>
       </c>
       <c r="M91" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N91" t="n">
         <v>30</v>
       </c>
       <c r="O91" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P91" t="n">
         <v>30</v>
@@ -8577,32 +8577,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>7278642452473317415</t>
+          <t>6857513639226640384</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0运城河东街万达店）</t>
+          <t>维也纳酒店（大同高铁站东信国际店）</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>维也纳酒店(山西运城河东街万达店)</t>
+          <t>维也纳酒店(大同高铁站东信国际店)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -8623,7 +8623,7 @@
         <v>10</v>
       </c>
       <c r="M92" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N92" t="n">
         <v>30</v>
@@ -8635,7 +8635,7 @@
         <v>30</v>
       </c>
       <c r="Q92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R92" t="n">
         <v>30</v>
@@ -8665,43 +8665,43 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>6601148990631184397</t>
+          <t>6601144225092339716</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>维也纳酒店（大同高铁站万达广场店）</t>
+          <t>锦江之星(平遥古城店)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>维也纳酒店(山西大同高铁站万达广场店)</t>
+          <t>锦江之星酒店(平遥古城店)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H93" t="n">
         <v>95</v>
       </c>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -8711,7 +8711,7 @@
         <v>10</v>
       </c>
       <c r="M93" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N93" t="n">
         <v>30</v>
@@ -8723,7 +8723,7 @@
         <v>30</v>
       </c>
       <c r="Q93" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R93" t="n">
         <v>30</v>
@@ -8753,27 +8753,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>6857513639226640384</t>
+          <t>6601138073352800270</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>维也纳酒店（大同高铁站东信国际店）</t>
+          <t>锦江之星品尚(太原平阳路店)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>维也纳酒店(大同高铁站东信国际店)</t>
+          <t>锦江之星品尚酒店(太原平阳路店)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -8799,19 +8799,19 @@
         <v>10</v>
       </c>
       <c r="M94" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N94" t="n">
         <v>30</v>
       </c>
       <c r="O94" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P94" t="n">
         <v>30</v>
       </c>
       <c r="Q94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R94" t="n">
         <v>30</v>
@@ -8841,27 +8841,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>晋城市</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>6601144225092339716</t>
+          <t>6601181102977583107</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>锦江之星(平遥古城店)</t>
+          <t>锦江之星酒店(晋城中原街店）</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>锦江之星酒店(平遥古城店)</t>
+          <t>锦江之星(晋城中原街店)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8887,13 +8887,13 @@
         <v>10</v>
       </c>
       <c r="M95" t="n">
+        <v>20</v>
+      </c>
+      <c r="N95" t="n">
+        <v>30</v>
+      </c>
+      <c r="O95" t="n">
         <v>25</v>
-      </c>
-      <c r="N95" t="n">
-        <v>30</v>
-      </c>
-      <c r="O95" t="n">
-        <v>20</v>
       </c>
       <c r="P95" t="n">
         <v>30</v>
@@ -8929,27 +8929,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>晋城市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>6601181102977583107</t>
+          <t>7389086049038764067</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>锦江之星酒店(晋城中原街店）</t>
+          <t>锦江之星（大同古城迎宾街酒店）</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>锦江之星(晋城中原街店)</t>
+          <t>锦江之星(大同古城迎宾街酒店)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8961,11 +8961,11 @@
         <v>95</v>
       </c>
       <c r="I96" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -8975,7 +8975,7 @@
         <v>10</v>
       </c>
       <c r="M96" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N96" t="n">
         <v>30</v>
@@ -8987,7 +8987,7 @@
         <v>30</v>
       </c>
       <c r="Q96" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R96" t="n">
         <v>30</v>
@@ -9017,27 +9017,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>7389086049038764067</t>
+          <t>7099792395503405059</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>锦江之星（大同古城迎宾街酒店）</t>
+          <t>锦江都城酒店(太原晋阳街地铁站店)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>锦江之星(大同古城迎宾街酒店)</t>
+          <t>锦江都城酒店(太原晋阳街店)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -9063,7 +9063,7 @@
         <v>10</v>
       </c>
       <c r="M97" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N97" t="n">
         <v>30</v>
@@ -9075,7 +9075,7 @@
         <v>30</v>
       </c>
       <c r="Q97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R97" t="n">
         <v>30</v>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9115,17 +9115,17 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>7099792395503405059</t>
+          <t>6946321582243448862</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>锦江都城酒店(太原晋阳街地铁站店)</t>
+          <t>麗枫酒店(太原高铁南站双塔寺北齐壁画博物馆店)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>锦江都城酒店(太原晋阳街店)</t>
+          <t>麗枫酒店(太原高铁南站建设南路店)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9157,13 +9157,13 @@
         <v>30</v>
       </c>
       <c r="O98" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P98" t="n">
         <v>30</v>
       </c>
       <c r="Q98" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R98" t="n">
         <v>30</v>
@@ -9203,22 +9203,22 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>6946321582243448862</t>
+          <t>7235081135372371972</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>麗枫酒店(太原高铁南站双塔寺北齐壁画博物馆店)</t>
+          <t>麗枫酒店（太原南站店）</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>麗枫酒店(太原高铁南站建设南路店)</t>
+          <t>麗枫酒店(太原南站店)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -9239,7 +9239,7 @@
         <v>10</v>
       </c>
       <c r="M99" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N99" t="n">
         <v>30</v>
@@ -9251,7 +9251,7 @@
         <v>30</v>
       </c>
       <c r="Q99" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R99" t="n">
         <v>30</v>
@@ -9291,22 +9291,22 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>7235081135372371972</t>
+          <t>7255337882926188598</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>麗枫酒店（太原南站店）</t>
+          <t>麗枫酒店（太原长风商务区晋阳湖店）</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>麗枫酒店(太原南站店)</t>
+          <t>麗枫酒店(太原万象城长风商务区店)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -9327,7 +9327,7 @@
         <v>10</v>
       </c>
       <c r="M100" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N100" t="n">
         <v>30</v>
@@ -9339,7 +9339,7 @@
         <v>30</v>
       </c>
       <c r="Q100" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R100" t="n">
         <v>30</v>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>7255337882926188598</t>
+          <t>6818215640046798863</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>麗枫酒店（太原长风商务区晋阳湖店）</t>
+          <t>麗枫酒店（太原长风街省政府茂业天地店）</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>麗枫酒店(太原万象城长风商务区店)</t>
+          <t>麗枫酒店(太原长风街省政府茂业天地店)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -9415,7 +9415,7 @@
         <v>10</v>
       </c>
       <c r="M101" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N101" t="n">
         <v>30</v>
@@ -9427,7 +9427,7 @@
         <v>30</v>
       </c>
       <c r="Q101" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R101" t="n">
         <v>30</v>
@@ -9457,27 +9457,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>6818215640046798863</t>
+          <t>7368725720052271167</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>麗枫酒店（太原长风街省政府茂业天地店）</t>
+          <t>丽怡酒店（大同古城店）</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>麗枫酒店(太原长风街省政府茂业天地店)</t>
+          <t>丽怡酒店(大同古城店)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9486,14 +9486,14 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -9503,19 +9503,19 @@
         <v>10</v>
       </c>
       <c r="M102" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N102" t="n">
         <v>30</v>
       </c>
       <c r="O102" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P102" t="n">
         <v>30</v>
       </c>
       <c r="Q102" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R102" t="n">
         <v>30</v>
@@ -9550,22 +9550,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>7368725720052271167</t>
+          <t>6601140766808999949</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>丽怡酒店（大同古城店）</t>
+          <t>喆啡酒店（忻州古城开来欣悦购物广场店）</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>丽怡酒店(大同古城店)</t>
+          <t>喆啡酒店(忻州和平路店)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9577,11 +9577,11 @@
         <v>97</v>
       </c>
       <c r="I103" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -9591,19 +9591,19 @@
         <v>10</v>
       </c>
       <c r="M103" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N103" t="n">
         <v>30</v>
       </c>
       <c r="O103" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P103" t="n">
         <v>30</v>
       </c>
       <c r="Q103" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R103" t="n">
         <v>30</v>
@@ -9633,27 +9633,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>6601140766808999949</t>
+          <t>6825490004949665792</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>喆啡酒店（忻州古城开来欣悦购物广场店）</t>
+          <t>维也纳国际酒店（太原迎泽大街下元地铁站公元时代城店）</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>喆啡酒店(忻州和平路店)</t>
+          <t>维也纳国际酒店(太原迎泽大街下元地铁站公元时代城店)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9685,13 +9685,13 @@
         <v>30</v>
       </c>
       <c r="O104" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P104" t="n">
         <v>30</v>
       </c>
       <c r="Q104" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R104" t="n">
         <v>30</v>
@@ -9721,32 +9721,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>6825490004949665792</t>
+          <t>7077026661430757414</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（太原迎泽大街下元地铁站公元时代城店）</t>
+          <t>麗枫酒店(大同高铁站方特店)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(太原迎泽大街下元地铁站公元时代城店)</t>
+          <t>麗枫酒店(大同高铁站方特店)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -9773,13 +9773,13 @@
         <v>30</v>
       </c>
       <c r="O105" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P105" t="n">
         <v>30</v>
       </c>
       <c r="Q105" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R105" t="n">
         <v>30</v>
@@ -9809,27 +9809,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>7077026661430757414</t>
+          <t>7067092710515017740</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>麗枫酒店(大同高铁站方特店)</t>
+          <t>7天优品Premium（长治壶关新建南路店）</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>麗枫酒店(大同高铁站方特店)</t>
+          <t>7天优品酒店(长治壶关新建南路店)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9838,14 +9838,14 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -9855,19 +9855,19 @@
         <v>10</v>
       </c>
       <c r="M106" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N106" t="n">
         <v>30</v>
       </c>
       <c r="O106" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P106" t="n">
         <v>30</v>
       </c>
       <c r="Q106" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R106" t="n">
         <v>30</v>
@@ -9902,38 +9902,38 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>7067092710515017740</t>
+          <t>6830714497225984000</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7天优品Premium（长治壶关新建南路店）</t>
+          <t>7天优品（晋中介休火车站绵山南街店）</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>7天优品酒店(长治壶关新建南路店)</t>
+          <t>7天优品(晋中介休火车站绵山南街店)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H107" t="n">
         <v>100</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -9943,13 +9943,13 @@
         <v>10</v>
       </c>
       <c r="M107" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N107" t="n">
         <v>30</v>
       </c>
       <c r="O107" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P107" t="n">
         <v>30</v>
@@ -9985,43 +9985,43 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>6830714497225984000</t>
+          <t>6883470080009570304</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>7天优品（晋中介休火车站绵山南街店）</t>
+          <t>7天酒店（临汾鼓楼南大街师大店）</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>7天优品(晋中介休火车站绵山南街店)</t>
+          <t>7天酒店(临汾鼓楼南大街师大店)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H108" t="n">
         <v>100</v>
       </c>
       <c r="I108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -10031,19 +10031,19 @@
         <v>10</v>
       </c>
       <c r="M108" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N108" t="n">
         <v>30</v>
       </c>
       <c r="O108" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P108" t="n">
         <v>30</v>
       </c>
       <c r="Q108" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R108" t="n">
         <v>30</v>
@@ -10078,22 +10078,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>6601142784051120131</t>
+          <t>6601148538246154244</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7天酒店(忻州古城市政府店)</t>
+          <t>7天酒店（大同火车站店）</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>7天酒店(忻州古城市政府店)</t>
+          <t>7天酒店(大同火车站店)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -10105,7 +10105,7 @@
         <v>100</v>
       </c>
       <c r="I109" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -10161,39 +10161,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>6883470080009570304</t>
+          <t>7232160323472459834</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7天酒店（临汾鼓楼南大街师大店）</t>
+          <t>7天酒店（长治上党区凯德世家广场店）</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>7天酒店(临汾鼓楼南大街师大店)</t>
+          <t>7天酒店(长治上党区府后东街店)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H110" t="n">
         <v>100</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -10207,13 +10207,13 @@
         <v>10</v>
       </c>
       <c r="M110" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N110" t="n">
         <v>30</v>
       </c>
       <c r="O110" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P110" t="n">
         <v>30</v>
@@ -10249,32 +10249,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>6601148538246154244</t>
+          <t>7234815855568095288</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>7天酒店（大同火车站店）</t>
+          <t>IU酒店（吕梁孝义万达广场市政府店）</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>7天酒店(大同火车站店)</t>
+          <t>IU酒店(孝义市政府店)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -10301,13 +10301,13 @@
         <v>30</v>
       </c>
       <c r="O111" t="n">
+        <v>20</v>
+      </c>
+      <c r="P111" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q111" t="n">
         <v>25</v>
-      </c>
-      <c r="P111" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>20</v>
       </c>
       <c r="R111" t="n">
         <v>30</v>
@@ -10337,27 +10337,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>7232160323472459834</t>
+          <t>7232915166617143353</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7天酒店（长治上党区凯德世家广场店）</t>
+          <t>IU酒店（太原南站东广场店）</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>7天酒店(长治上党区府后东街店)</t>
+          <t>IU酒店(太原南站东广场店)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10369,7 +10369,7 @@
         <v>100</v>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -10389,13 +10389,13 @@
         <v>30</v>
       </c>
       <c r="O112" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P112" t="n">
         <v>30</v>
       </c>
       <c r="Q112" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R112" t="n">
         <v>30</v>
@@ -10425,32 +10425,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>7234815855568095288</t>
+          <t>6917743132805171200</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IU酒店（吕梁孝义万达广场市政府店）</t>
+          <t>IU酒店（霍州署鼓楼西街店）</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>IU酒店(孝义市政府店)</t>
+          <t>IU酒店(霍州鼓楼店)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -10513,27 +10513,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>7232915166617143353</t>
+          <t>7333498258506909708</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IU酒店（太原南站东广场店）</t>
+          <t>丽怡酒店（平遥古城店）</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>IU酒店(太原南站东广场店)</t>
+          <t>丽怡酒店(平遥古城店)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10545,11 +10545,11 @@
         <v>100</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -10559,7 +10559,7 @@
         <v>10</v>
       </c>
       <c r="M114" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N114" t="n">
         <v>30</v>
@@ -10571,7 +10571,7 @@
         <v>30</v>
       </c>
       <c r="Q114" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R114" t="n">
         <v>30</v>
@@ -10601,32 +10601,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>7418425551997650980</t>
+          <t>7042656822482798629</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IU酒店（长治通天峡景区店）</t>
+          <t>凯里亚德酒店（太原晋阳湖万象城店）</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>IU酒店(长治通天峡景区店)</t>
+          <t>凯里亚德酒店(太原晋阳湖万象城店)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -10647,13 +10647,13 @@
         <v>10</v>
       </c>
       <c r="M115" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N115" t="n">
         <v>30</v>
       </c>
       <c r="O115" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P115" t="n">
         <v>30</v>
@@ -10689,27 +10689,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>6917743132805171200</t>
+          <t>7389122107235371019</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>IU酒店（霍州署鼓楼西街店）</t>
+          <t>喆啡酒店(平遥古城南门游客中心店)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>IU酒店(霍州鼓楼店)</t>
+          <t>喆啡酒店(平遥古城店)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10721,11 +10721,11 @@
         <v>100</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -10735,7 +10735,7 @@
         <v>10</v>
       </c>
       <c r="M116" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N116" t="n">
         <v>30</v>
@@ -10747,7 +10747,7 @@
         <v>30</v>
       </c>
       <c r="Q116" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R116" t="n">
         <v>30</v>
@@ -10777,43 +10777,43 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>7333498258506909708</t>
+          <t>7501791705801164815</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>丽怡酒店（平遥古城店）</t>
+          <t>喆啡酒店（大同古城华严寺店）</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>丽怡酒店(平遥古城店)</t>
+          <t>喆啡酒店(大同古城华严寺店)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H117" t="n">
         <v>100</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -10823,19 +10823,19 @@
         <v>10</v>
       </c>
       <c r="M117" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N117" t="n">
         <v>30</v>
       </c>
       <c r="O117" t="n">
+        <v>20</v>
+      </c>
+      <c r="P117" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q117" t="n">
         <v>25</v>
-      </c>
-      <c r="P117" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>15</v>
       </c>
       <c r="R117" t="n">
         <v>30</v>
@@ -10875,33 +10875,33 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>7042656822482798629</t>
+          <t>7051795666254694436</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（太原晋阳湖万象城店）</t>
+          <t>喆啡酒店（太原万象城店）</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(太原晋阳湖万象城店)</t>
+          <t>喆啡酒店(太原万象城店)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H118" t="n">
         <v>100</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -10911,13 +10911,13 @@
         <v>10</v>
       </c>
       <c r="M118" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N118" t="n">
         <v>30</v>
       </c>
       <c r="O118" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P118" t="n">
         <v>30</v>
@@ -10953,27 +10953,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>7389122107235371019</t>
+          <t>7662262592013862963</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>喆啡酒店(平遥古城南门游客中心店)</t>
+          <t>大同南站万达广场丽柏酒店</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>喆啡酒店(平遥古城店)</t>
+          <t>大同南站万达广场丽柏酒店</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10985,7 +10985,7 @@
         <v>100</v>
       </c>
       <c r="I119" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -11051,22 +11051,22 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>7501791705801164815</t>
+          <t>7401777865106130985</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>喆啡酒店（大同古城华严寺店）</t>
+          <t>大同古城丽柏酒店</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>喆啡酒店(大同古城华严寺店)</t>
+          <t>大同古城丽柏酒店</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -11087,19 +11087,19 @@
         <v>10</v>
       </c>
       <c r="M120" t="n">
+        <v>30</v>
+      </c>
+      <c r="N120" t="n">
+        <v>30</v>
+      </c>
+      <c r="O120" t="n">
         <v>25</v>
       </c>
-      <c r="N120" t="n">
-        <v>30</v>
-      </c>
-      <c r="O120" t="n">
-        <v>20</v>
-      </c>
       <c r="P120" t="n">
         <v>30</v>
       </c>
       <c r="Q120" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R120" t="n">
         <v>30</v>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -11139,29 +11139,29 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>7051795666254694436</t>
+          <t>6924420728850745347</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>喆啡酒店（太原万象城店）</t>
+          <t>希岸·轻雅酒店（太原平阳路茂业天地店）</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>喆啡酒店(太原万象城店)</t>
+          <t>希岸·轻雅酒店(太原平阳路亲贤街口店)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H121" t="n">
         <v>100</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -11181,13 +11181,13 @@
         <v>30</v>
       </c>
       <c r="O121" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P121" t="n">
         <v>30</v>
       </c>
       <c r="Q121" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R121" t="n">
         <v>30</v>
@@ -11217,27 +11217,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>山西北片区</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>大同市</t>
-        </is>
-      </c>
+          <t>山西中片区</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>7662262592013862963</t>
+          <t>7520530485496252462</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>大同南站万达广场丽柏酒店</t>
+          <t>平遥古城丽柏酒店</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>大同南站万达广场丽柏酒店</t>
+          <t>丽柏酒店(平遥古城店)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -11249,11 +11245,11 @@
         <v>100</v>
       </c>
       <c r="I122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -11263,19 +11259,19 @@
         <v>10</v>
       </c>
       <c r="M122" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N122" t="n">
         <v>30</v>
       </c>
       <c r="O122" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P122" t="n">
         <v>30</v>
       </c>
       <c r="Q122" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R122" t="n">
         <v>30</v>
@@ -11305,27 +11301,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>7401777865106130985</t>
+          <t>7277051619374532645</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>大同古城丽柏酒店</t>
+          <t>维也纳3好酒店(太原动物园店)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>大同古城丽柏酒店</t>
+          <t>维也纳3好酒店(太原动物园店)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -11337,7 +11333,7 @@
         <v>100</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -11393,27 +11389,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>6924420728850745347</t>
+          <t>7312687084538431499</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店（太原平阳路茂业天地店）</t>
+          <t>维也纳3好酒店(沁源胜利路政府店)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(太原平阳路亲贤街口店)</t>
+          <t>维也纳3好酒店(胜利路店)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11425,11 +11421,11 @@
         <v>100</v>
       </c>
       <c r="I124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -11439,13 +11435,13 @@
         <v>10</v>
       </c>
       <c r="M124" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N124" t="n">
         <v>30</v>
       </c>
       <c r="O124" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P124" t="n">
         <v>30</v>
@@ -11481,28 +11477,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>山西中片区</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>山西西片区</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>吕梁市</t>
+        </is>
+      </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>7520530485496252462</t>
+          <t>7449630764511004699</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>平遥古城丽柏酒店</t>
+          <t>维也纳3好酒店（吕梁临县柏桐苑凯瑞店）</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>丽柏酒店(平遥古城店)</t>
+          <t>维也纳3好酒店(吕梁临县柏桐苑店)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -11523,19 +11523,19 @@
         <v>10</v>
       </c>
       <c r="M125" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N125" t="n">
         <v>30</v>
       </c>
       <c r="O125" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P125" t="n">
         <v>30</v>
       </c>
       <c r="Q125" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="R125" t="n">
         <v>30</v>
@@ -11565,27 +11565,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>7312687084538431499</t>
+          <t>6919967936090228750</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(沁源胜利路政府店)</t>
+          <t>维也纳3好酒店（大同古城华严寺店）</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(胜利路店)</t>
+          <t>维也纳3好酒店(大同古城店)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11597,11 +11597,11 @@
         <v>100</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -11617,13 +11617,13 @@
         <v>30</v>
       </c>
       <c r="O126" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P126" t="n">
         <v>30</v>
       </c>
       <c r="Q126" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R126" t="n">
         <v>30</v>
@@ -11653,27 +11653,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>7449630764511004699</t>
+          <t>7264177468758558760</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（吕梁临县柏桐苑凯瑞店）</t>
+          <t>维也纳国际酒店(大同古城火车站店)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(吕梁临县柏桐苑店)</t>
+          <t>维也纳国际酒店(大同古城火车站店)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -11699,19 +11699,19 @@
         <v>10</v>
       </c>
       <c r="M127" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N127" t="n">
         <v>30</v>
       </c>
       <c r="O127" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P127" t="n">
         <v>30</v>
       </c>
       <c r="Q127" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="R127" t="n">
         <v>30</v>
@@ -11741,43 +11741,43 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>7264177468758558760</t>
+          <t>7045100153346197512</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(大同古城火车站店)</t>
+          <t>维也纳酒店（5.0太原综改区机场南站店）</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(大同古城火车站店)</t>
+          <t>维也纳酒店(5.0太原综改区机场南站店)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H128" t="n">
         <v>100</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -11787,13 +11787,13 @@
         <v>10</v>
       </c>
       <c r="M128" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N128" t="n">
         <v>30</v>
       </c>
       <c r="O128" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P128" t="n">
         <v>30</v>
@@ -11829,27 +11829,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>7045100153346197512</t>
+          <t>6601148990631184397</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0太原综改区机场南站店）</t>
+          <t>维也纳酒店（大同高铁站万达广场店）</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0太原综改区机场南站店)</t>
+          <t>维也纳酒店(山西大同高铁站万达广场店)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11861,11 +11861,11 @@
         <v>100</v>
       </c>
       <c r="I129" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -11875,13 +11875,13 @@
         <v>10</v>
       </c>
       <c r="M129" t="n">
+        <v>30</v>
+      </c>
+      <c r="N129" t="n">
+        <v>30</v>
+      </c>
+      <c r="O129" t="n">
         <v>25</v>
-      </c>
-      <c r="N129" t="n">
-        <v>30</v>
-      </c>
-      <c r="O129" t="n">
-        <v>30</v>
       </c>
       <c r="P129" t="n">
         <v>30</v>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -11927,33 +11927,33 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>6601131638728427523</t>
+          <t>6611416372956104717</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>锦江之星（太原柳巷大南门地铁站迎泽公园酒店）</t>
+          <t>锦江都城酒店（太原综改区太原学院店）</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>锦江之星(太原大南门地铁站迎泽公园店)</t>
+          <t>太原小店区太原学院锦江都城酒店</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H130" t="n">
         <v>100</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -11963,19 +11963,19 @@
         <v>10</v>
       </c>
       <c r="M130" t="n">
+        <v>30</v>
+      </c>
+      <c r="N130" t="n">
+        <v>30</v>
+      </c>
+      <c r="O130" t="n">
         <v>25</v>
       </c>
-      <c r="N130" t="n">
-        <v>30</v>
-      </c>
-      <c r="O130" t="n">
-        <v>20</v>
-      </c>
       <c r="P130" t="n">
         <v>30</v>
       </c>
       <c r="Q130" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R130" t="n">
         <v>30</v>
@@ -12626,54 +12626,54 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>7637699073047873570</t>
+          <t>7137101215036344334</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>麗枫酒店（长治东站八一广场店）</t>
+          <t>7天优品Premium（山西晋中太谷店）</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>麗枫酒店(长治东站八一广场店)</t>
+          <t>7天优品Premium(山西晋中太谷店)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>提质量,附加分,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K138" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L138" t="n">
         <v>10</v>
       </c>
       <c r="M138" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N138" t="n">
         <v>30</v>
       </c>
       <c r="O138" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P138" t="n">
         <v>30</v>
@@ -12685,7 +12685,7 @@
         <v>30</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T138" t="n">
         <v>20</v>
@@ -12709,27 +12709,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>7137101215036344334</t>
+          <t>6601179935497259011</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>7天优品Premium（山西晋中太谷店）</t>
+          <t>喆啡酒店（临汾向阳西路万达广场店）</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>7天优品Premium(山西晋中太谷店)</t>
+          <t>喆啡酒店(临汾向阳西路万达广场店)</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12741,11 +12741,11 @@
         <v>101</v>
       </c>
       <c r="I139" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,拿收益</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -12761,13 +12761,13 @@
         <v>30</v>
       </c>
       <c r="O139" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P139" t="n">
         <v>30</v>
       </c>
       <c r="Q139" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R139" t="n">
         <v>30</v>
@@ -12797,27 +12797,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>6601179935497259011</t>
+          <t>7278641696152242188</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>喆啡酒店（临汾向阳西路万达广场店）</t>
+          <t>IU酒店（忻州古城居然之家店）</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>喆啡酒店(临汾向阳西路万达广场店)</t>
+          <t>iu酒店(忻州居然之家店)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12826,36 +12826,36 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L140" t="n">
         <v>10</v>
       </c>
       <c r="M140" t="n">
+        <v>22</v>
+      </c>
+      <c r="N140" t="n">
+        <v>30</v>
+      </c>
+      <c r="O140" t="n">
         <v>25</v>
       </c>
-      <c r="N140" t="n">
-        <v>30</v>
-      </c>
-      <c r="O140" t="n">
-        <v>30</v>
-      </c>
       <c r="P140" t="n">
         <v>30</v>
       </c>
       <c r="Q140" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R140" t="n">
         <v>30</v>
@@ -12895,17 +12895,17 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>7278641696152242188</t>
+          <t>6679148759789602823</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>IU酒店（忻州古城居然之家店）</t>
+          <t>IU酒店（忻州古城高铁西站店）</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>iu酒店(忻州居然之家店)</t>
+          <t>IU酒店(忻州古城高铁西站店)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -12931,13 +12931,13 @@
         <v>10</v>
       </c>
       <c r="M141" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N141" t="n">
         <v>30</v>
       </c>
       <c r="O141" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P141" t="n">
         <v>30</v>
@@ -12973,27 +12973,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>6679148759789602823</t>
+          <t>7320489581046925352</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>IU酒店（忻州古城高铁西站店）</t>
+          <t>维也纳酒店（5.0长治学院高铁东站店）</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>IU酒店(忻州古城高铁西站店)</t>
+          <t>维也纳酒店(长治学院店)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -13019,7 +13019,7 @@
         <v>10</v>
       </c>
       <c r="M142" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N142" t="n">
         <v>30</v>
@@ -13031,7 +13031,7 @@
         <v>30</v>
       </c>
       <c r="Q142" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R142" t="n">
         <v>30</v>
@@ -13061,27 +13061,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>7320489581046925352</t>
+          <t>7247831339464919078</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0长治学院高铁东站店）</t>
+          <t>维也纳酒店（5.0霍州署香江城购物广场店）</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>维也纳酒店(长治学院店)</t>
+          <t>维也纳酒店(霍州香江城店)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -13113,13 +13113,13 @@
         <v>30</v>
       </c>
       <c r="O143" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P143" t="n">
         <v>30</v>
       </c>
       <c r="Q143" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R143" t="n">
         <v>30</v>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -13335,17 +13335,17 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>7062195246788151333</t>
+          <t>7637699073047873570</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>7天优品Premium（长治潞城888财富广场店）</t>
+          <t>麗枫酒店（长治东站八一广场店）</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>7天优品Premium·长治潞城888财富广场店</t>
+          <t>麗枫酒店(长治东站八一广场店)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -13354,14 +13354,14 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -13371,25 +13371,25 @@
         <v>10</v>
       </c>
       <c r="M146" t="n">
+        <v>30</v>
+      </c>
+      <c r="N146" t="n">
+        <v>30</v>
+      </c>
+      <c r="O146" t="n">
+        <v>20</v>
+      </c>
+      <c r="P146" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q146" t="n">
         <v>25</v>
       </c>
-      <c r="N146" t="n">
-        <v>30</v>
-      </c>
-      <c r="O146" t="n">
-        <v>30</v>
-      </c>
-      <c r="P146" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>20</v>
-      </c>
       <c r="R146" t="n">
         <v>30</v>
       </c>
       <c r="S146" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T146" t="n">
         <v>20</v>
@@ -13413,39 +13413,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>7425521749342554112</t>
+          <t>7062195246788151333</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>7天酒店（大同云冈恒安新区H区店）</t>
+          <t>7天优品Premium（长治潞城888财富广场店）</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>7天酒店(大同云冈恒安新区H区店)</t>
+          <t>7天优品Premium·长治潞城888财富广场店</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H147" t="n">
         <v>105</v>
       </c>
       <c r="I147" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -13506,22 +13506,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>7075171771309099049</t>
+          <t>6601142784051120131</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>IU酒店(大同云冈区南环西路阳光车城店）</t>
+          <t>7天酒店(忻州古城市政府店)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>IU酒店(大同阳光车城店)</t>
+          <t>7天酒店(忻州古城市政府店)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13533,7 +13533,7 @@
         <v>105</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -13589,39 +13589,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>7234821313162905615</t>
+          <t>7425521749342554112</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>IU酒店(汾阳杏花村酒店)</t>
+          <t>7天酒店（大同云冈恒安新区H区店）</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>IU酒店(山西汾阳市杏花村店)</t>
+          <t>7天酒店(大同云冈恒安新区H区店)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H149" t="n">
         <v>105</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -13677,43 +13677,43 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>7325070761364817961</t>
+          <t>7075171771309099049</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>IU酒店（临汾铝锅巷迎春南街店）</t>
+          <t>IU酒店(大同云冈区南环西路阳光车城店）</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>IU酒店(临汾迎春南街店)</t>
+          <t>IU酒店(大同阳光车城店)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H150" t="n">
         <v>105</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -13723,7 +13723,7 @@
         <v>10</v>
       </c>
       <c r="M150" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N150" t="n">
         <v>30</v>
@@ -13735,7 +13735,7 @@
         <v>30</v>
       </c>
       <c r="Q150" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R150" t="n">
         <v>30</v>
@@ -13765,27 +13765,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>7288552845555533859</t>
+          <t>7234821313162905615</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>IU酒店（长治屯留人民医院店）</t>
+          <t>IU酒店(汾阳杏花村酒店)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>IU酒店(长治屯留人民医院店)</t>
+          <t>IU酒店(山西汾阳市杏花村店)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13797,11 +13797,11 @@
         <v>105</v>
       </c>
       <c r="I151" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -13817,13 +13817,13 @@
         <v>30</v>
       </c>
       <c r="O151" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P151" t="n">
         <v>30</v>
       </c>
       <c r="Q151" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R151" t="n">
         <v>30</v>
@@ -13863,33 +13863,33 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>7039541568272861198</t>
+          <t>7325070761364817961</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>喆啡酒店（临汾生龙国际平阳广场店）</t>
+          <t>IU酒店（临汾铝锅巷迎春南街店）</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>喆啡酒店(临汾生龙国际平阳广场店)</t>
+          <t>IU酒店(临汾迎春南街店)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H152" t="n">
         <v>105</v>
       </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -13905,13 +13905,13 @@
         <v>30</v>
       </c>
       <c r="O152" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P152" t="n">
         <v>30</v>
       </c>
       <c r="Q152" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R152" t="n">
         <v>30</v>
@@ -13941,43 +13941,43 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>7604313299669829666</t>
+          <t>7288552845555533859</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>白玉兰酒店(大同南环西路万城中心店)</t>
+          <t>IU酒店（长治屯留人民医院店）</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>白玉兰酒店(大同南环西路万城中心店)</t>
+          <t>IU酒店(长治屯留人民医院店)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H153" t="n">
         <v>105</v>
       </c>
       <c r="I153" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K153" t="n">
@@ -13993,13 +13993,13 @@
         <v>30</v>
       </c>
       <c r="O153" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P153" t="n">
         <v>30</v>
       </c>
       <c r="Q153" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R153" t="n">
         <v>30</v>
@@ -14029,27 +14029,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>7277051619374532645</t>
+          <t>7039541568272861198</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(太原动物园店)</t>
+          <t>喆啡酒店（临汾生龙国际平阳广场店）</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(太原动物园店)</t>
+          <t>喆啡酒店(临汾生龙国际平阳广场店)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -14061,11 +14061,11 @@
         <v>105</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K154" t="n">
@@ -14075,13 +14075,13 @@
         <v>10</v>
       </c>
       <c r="M154" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N154" t="n">
         <v>30</v>
       </c>
       <c r="O154" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P154" t="n">
         <v>30</v>
@@ -14122,38 +14122,38 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>7097493988764026888</t>
+          <t>7604313299669829666</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（忻州保德同舟广场店）</t>
+          <t>白玉兰酒店(大同南环西路万城中心店)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(山西保德同舟广场店)</t>
+          <t>白玉兰酒店(大同南环西路万城中心店)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H155" t="n">
         <v>105</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -14163,13 +14163,13 @@
         <v>10</v>
       </c>
       <c r="M155" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N155" t="n">
         <v>30</v>
       </c>
       <c r="O155" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P155" t="n">
         <v>30</v>
@@ -14205,27 +14205,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>7233649472143394871</t>
+          <t>7097493988764026888</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0晋中榆次安宁街印象城店）</t>
+          <t>维也纳3好酒店（忻州保德同舟广场店）</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(晋中印象城万达广场店)</t>
+          <t>维也纳3好酒店(山西保德同舟广场店)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -14251,13 +14251,13 @@
         <v>10</v>
       </c>
       <c r="M156" t="n">
+        <v>30</v>
+      </c>
+      <c r="N156" t="n">
+        <v>30</v>
+      </c>
+      <c r="O156" t="n">
         <v>25</v>
-      </c>
-      <c r="N156" t="n">
-        <v>30</v>
-      </c>
-      <c r="O156" t="n">
-        <v>30</v>
       </c>
       <c r="P156" t="n">
         <v>30</v>
@@ -14293,32 +14293,32 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>7260353969937975333</t>
+          <t>7233649472143394871</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（忻州雁门大道店）</t>
+          <t>维也纳国际酒店（5.0晋中榆次安宁街印象城店）</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(忻州雁门大道店)</t>
+          <t>维也纳国际酒店(晋中印象城万达广场店)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H157" t="n">
@@ -14381,27 +14381,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>7131300990695540739</t>
+          <t>7260353969937975333</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0 太原长风西街万象城店）</t>
+          <t>维也纳国际酒店（忻州雁门大道店）</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>维也纳酒店(太原长风西街万象城店)</t>
+          <t>维也纳国际酒店(忻州雁门大道店)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K158" t="n">
@@ -14427,13 +14427,13 @@
         <v>10</v>
       </c>
       <c r="M158" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N158" t="n">
         <v>30</v>
       </c>
       <c r="O158" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P158" t="n">
         <v>30</v>
@@ -14469,32 +14469,32 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>7313819468308219956</t>
+          <t>7131300990695540739</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0大同古城云冈同煤总医院煤业店）</t>
+          <t>维也纳酒店（5.0 太原长风西街万象城店）</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0大同古城云冈同煤总医院煤业店)</t>
+          <t>维也纳酒店(太原长风西街万象城店)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -14557,27 +14557,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>晋城市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>7498181324855838755</t>
+          <t>7313819468308219956</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0晋城经济开发区兰花路店）</t>
+          <t>维也纳酒店（5.0大同古城云冈同煤总医院煤业店）</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>维也纳酒店(晋城经济开发区兰花路店)</t>
+          <t>维也纳酒店(5.0大同古城云冈同煤总医院煤业店)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -14589,11 +14589,11 @@
         <v>105</v>
       </c>
       <c r="I160" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K160" t="n">
@@ -14603,13 +14603,13 @@
         <v>10</v>
       </c>
       <c r="M160" t="n">
+        <v>30</v>
+      </c>
+      <c r="N160" t="n">
+        <v>30</v>
+      </c>
+      <c r="O160" t="n">
         <v>25</v>
-      </c>
-      <c r="N160" t="n">
-        <v>30</v>
-      </c>
-      <c r="O160" t="n">
-        <v>30</v>
       </c>
       <c r="P160" t="n">
         <v>30</v>
@@ -14650,22 +14650,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>晋城市</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>7493356975233861671</t>
+          <t>7498181324855838755</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0深化版运城北站吾悦广场店）</t>
+          <t>维也纳酒店（5.0晋城经济开发区兰花路店）</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>维也纳酒店(运城北站店)</t>
+          <t>维也纳酒店(晋城经济开发区兰花路店)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -14677,11 +14677,11 @@
         <v>105</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K161" t="n">
@@ -14697,13 +14697,13 @@
         <v>30</v>
       </c>
       <c r="O161" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P161" t="n">
         <v>30</v>
       </c>
       <c r="Q161" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R161" t="n">
         <v>30</v>
@@ -14733,32 +14733,32 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>6601138956849383438</t>
+          <t>7493356975233861671</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>锦江之星(太原清徐东湖公园店)</t>
+          <t>维也纳酒店（5.0深化版运城北站吾悦广场店）</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>锦江之星酒店(清徐东湖公园店)</t>
+          <t>维也纳酒店(运城北站店)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H162" t="n">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -14785,13 +14785,13 @@
         <v>30</v>
       </c>
       <c r="O162" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P162" t="n">
         <v>30</v>
       </c>
       <c r="Q162" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R162" t="n">
         <v>30</v>
@@ -14821,27 +14821,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>7417336175620278291</t>
+          <t>6601138956849383438</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>锦江之星（大同南站东信万达广场店）</t>
+          <t>锦江之星(太原清徐东湖公园店)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>锦江之星酒店(大同南站东信广场店)</t>
+          <t>锦江之星酒店(清徐东湖公园店)</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -14853,7 +14853,7 @@
         <v>105</v>
       </c>
       <c r="I163" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -15007,33 +15007,33 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>6601148040021559299</t>
+          <t>6601131638728427523</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>锦江之星（太原柳巷钟楼街府西街地铁站酒店）</t>
+          <t>锦江之星（太原柳巷大南门地铁站迎泽公园酒店）</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>锦江之星(太原府西街地铁站店)</t>
+          <t>锦江之星(太原大南门地铁站迎泽公园店)</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H165" t="n">
         <v>105</v>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K165" t="n">
@@ -15043,13 +15043,13 @@
         <v>10</v>
       </c>
       <c r="M165" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N165" t="n">
         <v>30</v>
       </c>
       <c r="O165" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P165" t="n">
         <v>30</v>
@@ -15085,7 +15085,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -15095,17 +15095,17 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>6611416372956104717</t>
+          <t>6601148040021559299</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>锦江都城酒店（太原综改区太原学院店）</t>
+          <t>锦江之星（太原柳巷钟楼街府西街地铁站酒店）</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>太原小店区太原学院锦江都城酒店</t>
+          <t>锦江之星(太原府西街地铁站店)</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -15137,13 +15137,13 @@
         <v>30</v>
       </c>
       <c r="O166" t="n">
+        <v>20</v>
+      </c>
+      <c r="P166" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q166" t="n">
         <v>25</v>
-      </c>
-      <c r="P166" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>20</v>
       </c>
       <c r="R166" t="n">
         <v>30</v>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H170" t="n">
@@ -15613,27 +15613,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>7247831339464919078</t>
+          <t>7505410903254829071</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0霍州署香江城购物广场店）</t>
+          <t>凯里亚德酒店（大同古城大润发店）</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>维也纳酒店(霍州香江城店)</t>
+          <t>凯里亚德酒店(大同西环路大润发店)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -15642,14 +15642,14 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I172" t="n">
         <v>5</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -15659,19 +15659,19 @@
         <v>10</v>
       </c>
       <c r="M172" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N172" t="n">
         <v>30</v>
       </c>
       <c r="O172" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P172" t="n">
         <v>30</v>
       </c>
       <c r="Q172" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R172" t="n">
         <v>30</v>
@@ -15706,38 +15706,38 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>朔州市</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>7505410903254829071</t>
+          <t>7255874167298328628</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（大同古城大润发店）</t>
+          <t>潮漫酒店(朔州应县木塔店)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(大同西环路大润发店)</t>
+          <t>潮漫酒店(朔州应县木塔店)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H173" t="n">
         <v>110</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K173" t="n">
@@ -15753,13 +15753,13 @@
         <v>30</v>
       </c>
       <c r="O173" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P173" t="n">
         <v>30</v>
       </c>
       <c r="Q173" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R173" t="n">
         <v>30</v>
@@ -15789,27 +15789,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西南片区</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>朔州市</t>
+          <t>晋城市</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>7255874167298328628</t>
+          <t>7369839537406609434</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>潮漫酒店(朔州应县木塔店)</t>
+          <t>潮漫酒店（晋城中原新城店）</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>潮漫酒店(朔州应县木塔店)</t>
+          <t>潮漫酒店(晋城中原新城店)</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -15877,39 +15877,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>山西南片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>晋城市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>7369839537406609434</t>
+          <t>7484835868985788428</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>潮漫酒店（晋城中原新城店）</t>
+          <t>白玉兰商务酒店(晋中灵石王家大院新建街店)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>潮漫酒店(晋城中原新城店)</t>
+          <t>锦江白玉兰商务酒店(晋中灵石王家大院新建街店)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H175" t="n">
         <v>110</v>
       </c>
       <c r="I175" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -15975,17 +15975,17 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>7484835868985788428</t>
+          <t>6636210480207644676</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(晋中灵石王家大院新建街店)</t>
+          <t>白玉兰酒店(平遥古城南门店)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>锦江白玉兰商务酒店(晋中灵石王家大院新建街店)</t>
+          <t>白玉兰酒店(平遥古城南门店)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -15997,7 +15997,7 @@
         <v>110</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -16053,27 +16053,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>6636210480207644676</t>
+          <t>7119712870631213088</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>白玉兰酒店(平遥古城南门店)</t>
+          <t>维也纳3好酒店（五台山店）</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>白玉兰酒店(平遥古城南门店)</t>
+          <t>维也纳3好酒店(五台山店)</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -16105,13 +16105,13 @@
         <v>30</v>
       </c>
       <c r="O177" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P177" t="n">
         <v>30</v>
       </c>
       <c r="Q177" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R177" t="n">
         <v>30</v>
@@ -16141,27 +16141,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>7119712870631213088</t>
+          <t>7241433886763255864</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（五台山店）</t>
+          <t>维也纳国际酒店(山西博物院省心血管医院店)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(五台山店)</t>
+          <t>维也纳国际酒店(漪汾店)</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -16239,17 +16239,17 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>7241433886763255864</t>
+          <t>6601208604697577476</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(山西博物院省心血管医院店)</t>
+          <t>维也纳国际酒店（太原高铁南站武宿机场店）</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(漪汾店)</t>
+          <t>维也纳国际酒店(太原高铁南站武宿机场店)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -16317,27 +16317,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西中片区</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>6601208604697577476</t>
+          <t>6601144801003833352</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（太原高铁南站武宿机场店）</t>
+          <t>锦江之星(长治八一广场城隍庙店)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(太原高铁南站武宿机场店)</t>
+          <t>锦江之星(长治八一广场店)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量</t>
         </is>
       </c>
       <c r="K180" t="n">
@@ -16369,13 +16369,13 @@
         <v>30</v>
       </c>
       <c r="O180" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P180" t="n">
         <v>30</v>
       </c>
       <c r="Q180" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R180" t="n">
         <v>30</v>
@@ -16405,27 +16405,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>山西中片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>6601144801003833352</t>
+          <t>7417336175620278291</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>锦江之星(长治八一广场城隍庙店)</t>
+          <t>锦江之星（大同南站东信万达广场店）</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>锦江之星(长治八一广场店)</t>
+          <t>锦江之星酒店(大同南站东信广场店)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -16437,11 +16437,11 @@
         <v>110</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>提质量</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K181" t="n">
@@ -16451,19 +16451,19 @@
         <v>10</v>
       </c>
       <c r="M181" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N181" t="n">
         <v>30</v>
       </c>
       <c r="O181" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P181" t="n">
         <v>30</v>
       </c>
       <c r="Q181" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R181" t="n">
         <v>30</v>
@@ -17285,39 +17285,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>山西西片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>7295277091782658067</t>
+          <t>6875202341230987277</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>IU酒店（太原山西博物院省心血管医院店）</t>
+          <t>凯里亚德酒店（大同高铁站方特店）</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>IU酒店(太原漪汾街心血管医院店)</t>
+          <t>凯里亚德酒店(大同高铁站方特店)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H191" t="n">
         <v>115</v>
       </c>
       <c r="I191" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -17383,22 +17383,22 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>6875202341230987277</t>
+          <t>6950029908072466439</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（大同高铁站方特店）</t>
+          <t>潮漫酒店(大同灵丘汽车站高速口店)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(大同高铁站方特店)</t>
+          <t>潮漫酒店(大同灵丘汽车站店)</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H192" t="n">
@@ -17466,34 +17466,34 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>朔州市</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>6950029908072466439</t>
+          <t>7446650920168851465</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>潮漫酒店(大同灵丘汽车站高速口店)</t>
+          <t>维也纳酒店(5.0朔州山阴南站御龙国际店)</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>潮漫酒店(大同灵丘汽车站店)</t>
+          <t>维也纳酒店(5.0朔州山阴南站御龙国际酒店)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H193" t="n">
         <v>115</v>
       </c>
       <c r="I193" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -17549,27 +17549,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西东片区</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>朔州市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>7446650920168851465</t>
+          <t>6601139930582222856</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0朔州山阴南站御龙国际店)</t>
+          <t>锦江之星风尚（太原柳巷大南门地铁站酒店）</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0朔州山阴南站御龙国际酒店)</t>
+          <t>锦江之星风尚(太原柳巷钟楼街大南门地铁站酒店)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -17585,7 +17585,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量</t>
         </is>
       </c>
       <c r="K194" t="n">
@@ -17601,13 +17601,13 @@
         <v>30</v>
       </c>
       <c r="O194" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P194" t="n">
         <v>30</v>
       </c>
       <c r="Q194" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R194" t="n">
         <v>30</v>
@@ -17637,32 +17637,32 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>山西东片区</t>
+          <t>山西北片区</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>朔州市</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>6601139930582222856</t>
+          <t>7363890716516288550</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>锦江之星风尚（太原柳巷大南门地铁站酒店）</t>
+          <t>锦江之星（朔州老城豪德广场店）</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>锦江之星风尚(太原柳巷钟楼街大南门地铁站酒店)</t>
+          <t>锦江之星酒店(朔州老城马邑路店)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H195" t="n">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>提质量</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K195" t="n">
@@ -17683,13 +17683,13 @@
         <v>10</v>
       </c>
       <c r="M195" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N195" t="n">
         <v>30</v>
       </c>
       <c r="O195" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P195" t="n">
         <v>30</v>
@@ -17725,32 +17725,32 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>山西北片区</t>
+          <t>山西西片区</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>朔州市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>7363890716516288550</t>
+          <t>7317553243150632994</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>锦江之星（朔州老城豪德广场店）</t>
+          <t>麗枫酒店（吕梁柳林店）</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>锦江之星酒店(朔州老城马邑路店)</t>
+          <t>丽枫酒店(吕梁柳林店)</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H196" t="n">
@@ -17818,38 +17818,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>7317553243150632994</t>
+          <t>6601141370759415815</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>麗枫酒店（吕梁柳林店）</t>
+          <t>7天酒店（山西白求恩医院西门店）</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>丽枫酒店(吕梁柳林店)</t>
+          <t>7天酒店(山西白求恩医院西门店)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -17859,7 +17859,7 @@
         <v>10</v>
       </c>
       <c r="M197" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N197" t="n">
         <v>30</v>
@@ -17911,17 +17911,17 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>6601141370759415815</t>
+          <t>7295277091782658067</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>7天酒店（山西白求恩医院西门店）</t>
+          <t>IU酒店（太原山西博物院省心血管医院店）</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>7天酒店(山西白求恩医院西门店)</t>
+          <t>IU酒店(太原漪汾街心血管医院店)</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -17933,7 +17933,7 @@
         <v>120</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>120</v>
       </c>
       <c r="I201" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
